--- a/data/trans_dic/P57GLOBAL_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P57GLOBAL_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (tasa de respuesta: 98,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73,72; 79,95</t>
+          <t>73,67; 80,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,68; 68,19</t>
+          <t>60,46; 67,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,29; 82,67</t>
+          <t>76,08; 82,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54,13; 62,95</t>
+          <t>53,86; 62,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,28; 80,51</t>
+          <t>74,51; 80,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,58; 75,56</t>
+          <t>68,62; 75,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,99; 87,66</t>
+          <t>81,91; 87,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>59,18; 65,57</t>
+          <t>58,92; 65,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>75,05; 79,57</t>
+          <t>74,98; 79,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65,65; 70,83</t>
+          <t>65,92; 70,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80,17; 84,32</t>
+          <t>80,12; 84,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>57,79; 63,31</t>
+          <t>57,66; 62,92</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,8; 73,1</t>
+          <t>67,07; 72,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>65,53; 71,45</t>
+          <t>65,45; 71,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78,63; 83,73</t>
+          <t>79,04; 83,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,39; 66,03</t>
+          <t>22,88; 65,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>70,7; 76,67</t>
+          <t>71,03; 76,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,27; 77,6</t>
+          <t>71,84; 77,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,09; 88,59</t>
+          <t>84,49; 88,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>65,02; 70,34</t>
+          <t>65,14; 70,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>69,88; 73,99</t>
+          <t>70,06; 74,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69,59; 73,73</t>
+          <t>69,68; 73,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82,17; 85,54</t>
+          <t>82,36; 85,77</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,64; 67,16</t>
+          <t>38,3; 67,11</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60,55; 68,32</t>
+          <t>61,06; 68,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,24; 69,44</t>
+          <t>62,66; 70,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83,42; 88,61</t>
+          <t>83,33; 88,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62,13; 70,67</t>
+          <t>61,51; 70,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,35; 71,1</t>
+          <t>64,26; 70,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,87; 73,41</t>
+          <t>66,38; 73,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82,88; 88,2</t>
+          <t>83,35; 88,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52,14; 66,98</t>
+          <t>53,11; 66,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63,74; 68,91</t>
+          <t>63,45; 68,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65,58; 70,55</t>
+          <t>65,41; 70,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>84,05; 87,85</t>
+          <t>84,22; 87,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59,17; 67,46</t>
+          <t>58,95; 67,45</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,94; 72,82</t>
+          <t>66,72; 72,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>71,02; 77,15</t>
+          <t>71,63; 77,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,88; 83,02</t>
+          <t>77,62; 82,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58,12; 65,56</t>
+          <t>57,98; 65,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,85; 73,38</t>
+          <t>67,75; 73,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,25; 84,08</t>
+          <t>79,3; 84,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,68; 84,48</t>
+          <t>79,79; 84,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45,3; 62,86</t>
+          <t>46,28; 63,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>68,02; 72,19</t>
+          <t>68,21; 72,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76,38; 80,21</t>
+          <t>76,3; 80,15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79,8; 83,19</t>
+          <t>79,64; 83,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51,83; 62,63</t>
+          <t>53,26; 62,9</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>68,81; 71,98</t>
+          <t>68,8; 72,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67,33; 70,42</t>
+          <t>67,28; 70,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,69; 83,38</t>
+          <t>80,46; 83,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44,53; 63,76</t>
+          <t>43,82; 63,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>70,65; 73,61</t>
+          <t>70,66; 73,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,71; 76,73</t>
+          <t>73,78; 76,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,36; 85,93</t>
+          <t>83,5; 86,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>58,44; 64,94</t>
+          <t>57,68; 64,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>70,14; 72,39</t>
+          <t>70,2; 72,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70,94; 73,25</t>
+          <t>71,07; 73,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82,45; 84,33</t>
+          <t>82,49; 84,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,76; 63,52</t>
+          <t>51,86; 63,55</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (tasa de respuesta: 98,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>511638; 554857</t>
+          <t>511259; 556628</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>421113; 473203</t>
+          <t>419590; 470465</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>512478; 555314</t>
+          <t>511056; 554554</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>338952; 394150</t>
+          <t>337265; 394368</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>510587; 553357</t>
+          <t>512118; 553664</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>474101; 522351</t>
+          <t>474434; 523941</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>547750; 585619</t>
+          <t>547234; 585564</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>389031; 431016</t>
+          <t>387323; 430325</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1036701; 1099177</t>
+          <t>1035744; 1096149</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>909517; 981174</t>
+          <t>913134; 980066</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1074094; 1129723</t>
+          <t>1073460; 1128350</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>741707; 812629</t>
+          <t>740102; 807581</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>641787; 702247</t>
+          <t>644329; 699051</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>660016; 719651</t>
+          <t>659294; 723368</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>799052; 850878</t>
+          <t>803288; 853426</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>334768; 778747</t>
+          <t>269845; 776613</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>683858; 741563</t>
+          <t>686996; 740596</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>729735; 794500</t>
+          <t>735568; 796092</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>870135; 916740</t>
+          <t>874333; 915370</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>612574; 662683</t>
+          <t>613722; 664048</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1347183; 1426459</t>
+          <t>1350813; 1427974</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1413391; 1497498</t>
+          <t>1415226; 1499365</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1685257; 1754548</t>
+          <t>1689269; 1759292</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>819664; 1424825</t>
+          <t>812531; 1423681</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>409783; 462368</t>
+          <t>413213; 464263</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>464597; 518328</t>
+          <t>467736; 522614</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>625340; 664227</t>
+          <t>624640; 665501</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>433295; 492818</t>
+          <t>428949; 491728</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>440034; 486217</t>
+          <t>439438; 485078</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>516713; 567250</t>
+          <t>512937; 567461</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>640069; 681149</t>
+          <t>643684; 682504</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>375687; 482681</t>
+          <t>382678; 481850</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>867204; 937574</t>
+          <t>863318; 933798</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>996261; 1071765</t>
+          <t>993743; 1072219</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1279088; 1337016</t>
+          <t>1281722; 1336541</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>839081; 956576</t>
+          <t>835873; 956366</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>628518; 683800</t>
+          <t>626457; 680524</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>666606; 724176</t>
+          <t>672338; 723997</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>724612; 772464</t>
+          <t>722230; 771785</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>527801; 595335</t>
+          <t>526530; 590616</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>703997; 761389</t>
+          <t>702980; 759742</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>820194; 870211</t>
+          <t>820732; 870628</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>823572; 873214</t>
+          <t>824758; 874637</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>484682; 672553</t>
+          <t>495158; 674904</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1344423; 1426942</t>
+          <t>1348290; 1426122</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1507358; 1583041</t>
+          <t>1505774; 1581857</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1567231; 1633854</t>
+          <t>1564094; 1634776</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1025185; 1238912</t>
+          <t>1053475; 1244178</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2250542; 2354164</t>
+          <t>2250039; 2355032</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2280017; 2384626</t>
+          <t>2278392; 2391339</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2717762; 2808146</t>
+          <t>2709949; 2805215</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1518941; 2174881</t>
+          <t>1494593; 2170174</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2385333; 2485211</t>
+          <t>2385562; 2491086</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2596683; 2703225</t>
+          <t>2599356; 2702639</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2924839; 3015188</t>
+          <t>2929722; 3018733</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1980925; 2201273</t>
+          <t>1955444; 2194019</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4661791; 4811229</t>
+          <t>4665905; 4815066</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4901721; 5060829</t>
+          <t>4910688; 5064090</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5669921; 5799050</t>
+          <t>5672689; 5791798</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3520377; 4320061</t>
+          <t>3527222; 4322024</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57GLOBAL_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P57GLOBAL_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>61,18%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73,67; 80,2</t>
+          <t>73,93; 80,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,46; 67,79</t>
+          <t>60,7; 68,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,08; 82,56</t>
+          <t>76,26; 82,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53,86; 62,98</t>
+          <t>54,78; 63,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,51; 80,55</t>
+          <t>73,92; 80,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,62; 75,79</t>
+          <t>68,34; 75,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,91; 87,65</t>
+          <t>82,12; 87,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>58,92; 65,46</t>
+          <t>59,46; 65,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74,98; 79,35</t>
+          <t>74,81; 79,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65,92; 70,75</t>
+          <t>65,92; 70,9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80,12; 84,22</t>
+          <t>80,06; 84,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>57,66; 62,92</t>
+          <t>58,43; 63,87</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>67,41%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>67,07; 72,76</t>
+          <t>67,29; 73,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>65,45; 71,82</t>
+          <t>65,84; 71,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,04; 83,98</t>
+          <t>78,8; 83,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,88; 65,85</t>
+          <t>62,53; 69,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>71,03; 76,57</t>
+          <t>71,26; 76,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,84; 77,75</t>
+          <t>71,77; 77,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,49; 88,46</t>
+          <t>84,33; 88,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>65,14; 70,49</t>
+          <t>66,0; 71,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>70,06; 74,07</t>
+          <t>69,89; 74,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69,68; 73,82</t>
+          <t>69,76; 73,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82,36; 85,77</t>
+          <t>82,25; 85,67</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,3; 67,11</t>
+          <t>65,1; 69,39</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>66,71%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61,06; 68,6</t>
+          <t>60,76; 68,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,66; 70,01</t>
+          <t>62,48; 69,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83,33; 88,78</t>
+          <t>83,62; 88,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61,51; 70,51</t>
+          <t>63,72; 71,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,26; 70,93</t>
+          <t>64,31; 70,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,38; 73,44</t>
+          <t>66,5; 73,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83,35; 88,38</t>
+          <t>83,07; 88,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53,11; 66,87</t>
+          <t>62,84; 69,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63,45; 68,63</t>
+          <t>63,49; 68,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65,41; 70,58</t>
+          <t>65,63; 70,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>84,22; 87,82</t>
+          <t>84,35; 87,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>58,95; 67,45</t>
+          <t>64,24; 69,28</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>63,27%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,72; 72,47</t>
+          <t>66,89; 72,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>71,63; 77,13</t>
+          <t>71,55; 77,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,62; 82,95</t>
+          <t>77,94; 83,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57,98; 65,04</t>
+          <t>60,16; 66,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,75; 73,22</t>
+          <t>67,67; 73,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,3; 84,12</t>
+          <t>79,13; 84,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,79; 84,62</t>
+          <t>79,72; 84,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,28; 63,08</t>
+          <t>60,46; 65,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>68,21; 72,15</t>
+          <t>68,2; 72,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76,3; 80,15</t>
+          <t>76,46; 79,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79,64; 83,23</t>
+          <t>79,56; 83,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,26; 62,9</t>
+          <t>61,34; 65,42</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>64,84%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>68,8; 72,01</t>
+          <t>68,69; 71,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67,28; 70,62</t>
+          <t>67,23; 70,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,46; 83,29</t>
+          <t>80,47; 83,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43,82; 63,62</t>
+          <t>62,57; 66,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>70,66; 73,79</t>
+          <t>70,83; 73,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,78; 76,72</t>
+          <t>73,9; 76,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,5; 86,03</t>
+          <t>83,39; 85,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>57,68; 64,72</t>
+          <t>63,9; 66,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>70,2; 72,44</t>
+          <t>70,27; 72,46</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71,07; 73,29</t>
+          <t>71,04; 73,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82,49; 84,22</t>
+          <t>82,36; 84,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,86; 63,55</t>
+          <t>63,67; 66,08</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>366661</t>
+          <t>405079</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>410341</t>
+          <t>448388</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>777003</t>
+          <t>853467</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>511259; 556628</t>
+          <t>513082; 555945</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>419590; 470465</t>
+          <t>421203; 472872</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>511056; 554554</t>
+          <t>512229; 554624</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>337265; 394368</t>
+          <t>372942; 431446</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>512118; 553664</t>
+          <t>508065; 552608</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>474434; 523941</t>
+          <t>472438; 521279</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>547234; 585564</t>
+          <t>548632; 583832</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>387323; 430325</t>
+          <t>424670; 470471</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1035744; 1096149</t>
+          <t>1033362; 1097550</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>913134; 980066</t>
+          <t>913222; 982234</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1073460; 1128350</t>
+          <t>1072587; 1128842</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>740102; 807581</t>
+          <t>815118; 891013</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>606276</t>
+          <t>680774</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>639036</t>
+          <t>725136</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1245312</t>
+          <t>1405910</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>644329; 699051</t>
+          <t>646433; 703415</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>659294; 723368</t>
+          <t>663195; 724045</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>803288; 853426</t>
+          <t>800775; 852259</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>269845; 776613</t>
+          <t>646095; 715267</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>686996; 740596</t>
+          <t>689290; 741373</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>735568; 796092</t>
+          <t>734821; 795044</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>874333; 915370</t>
+          <t>872656; 914033</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>613722; 664048</t>
+          <t>694546; 749760</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1350813; 1427974</t>
+          <t>1347403; 1428872</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1415226; 1499365</t>
+          <t>1416913; 1498791</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1689269; 1759292</t>
+          <t>1686977; 1757122</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>812531; 1423681</t>
+          <t>1357808; 1447267</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>462449</t>
+          <t>536061</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>450379</t>
+          <t>527798</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>912828</t>
+          <t>1063860</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>413213; 464263</t>
+          <t>411182; 464361</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>467736; 522614</t>
+          <t>466413; 519194</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>624640; 665501</t>
+          <t>626847; 663815</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>428949; 491728</t>
+          <t>505426; 567972</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>439438; 485078</t>
+          <t>439782; 485214</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>512937; 567461</t>
+          <t>513858; 568381</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>643684; 682504</t>
+          <t>641505; 681175</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>382678; 481850</t>
+          <t>503663; 553731</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>863318; 933798</t>
+          <t>863857; 935990</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>993743; 1072219</t>
+          <t>997001; 1073559</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1281722; 1336541</t>
+          <t>1283723; 1337252</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>835873; 956366</t>
+          <t>1024536; 1104925</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>561085</t>
+          <t>616291</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>620308</t>
+          <t>691012</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1181393</t>
+          <t>1307304</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>626457; 680524</t>
+          <t>628083; 683223</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>672338; 723997</t>
+          <t>671601; 726334</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>722230; 771785</t>
+          <t>725151; 774445</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>526530; 590616</t>
+          <t>584671; 648776</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>702980; 759742</t>
+          <t>702115; 760777</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>820732; 870628</t>
+          <t>818944; 869743</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>824758; 874637</t>
+          <t>824013; 872790</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>495158; 674904</t>
+          <t>661683; 719791</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1348290; 1426122</t>
+          <t>1348145; 1427209</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1505774; 1581857</t>
+          <t>1508996; 1577776</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1564094; 1634776</t>
+          <t>1562557; 1632908</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1053475; 1244178</t>
+          <t>1267513; 1351774</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1996471</t>
+          <t>2238205</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2120065</t>
+          <t>2392335</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4116536</t>
+          <t>4630539</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2250039; 2355032</t>
+          <t>2246459; 2354550</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2278392; 2391339</t>
+          <t>2276496; 2387681</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2709949; 2805215</t>
+          <t>2710225; 2804228</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1494593; 2170174</t>
+          <t>2176876; 2301574</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2385562; 2491086</t>
+          <t>2391150; 2493440</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2599356; 2702639</t>
+          <t>2603273; 2701715</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2929722; 3018733</t>
+          <t>2925991; 3014856</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1955444; 2194019</t>
+          <t>2340477; 2443956</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4665905; 4815066</t>
+          <t>4670773; 4816316</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4910688; 5064090</t>
+          <t>4908312; 5063081</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5672689; 5791798</t>
+          <t>5663488; 5792360</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3527222; 4322024</t>
+          <t>4547219; 4719049</t>
         </is>
       </c>
     </row>
